--- a/site/exports/nudt-systems.xlsx
+++ b/site/exports/nudt-systems.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分职业资料：已核岗位与教学，求学履历待核；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：多媒体应用技术；主讲或建设课程；教学／课程开设时间：2002；正文明确2002年牵头开设该公共选修课；不是任职起点。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm | 程序设计与数据结构；主讲或建设课程；教学／课程开设时间：时间未披露；官方教学报道；无课程全文或学生信息。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm | 大数据分析；主讲或建设课程；教学／课程开设时间：时间未披露；官方教学报道；无课程全文或学生信息。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm</t>
+          <t>分批核实资料，不是完整名录；部分职业资料：已核岗位与教学，求学履历待核；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：多媒体应用技术；主讲或建设课程；教学／课程开设时间：2002；正文明确2002年牵头开设该公共选修课；不是任职起点。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm | 程序设计与数据结构；主讲或建设课程；教学／课程开设时间：时间未披露；官方教学报道；无课程全文或学生信息。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm | 大数据分析；主讲或建设课程；教学／课程开设时间：时间未披露；官方教学报道；无课程全文或学生信息。；来源ID：weiyingmei-source-2；https://www.nudt.edu.cn/rwfc/776b991e16eb471ba84fd6587e017b8f.htm；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
